--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
@@ -15589,7 +15589,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rezago respecto a la población de 6 a 21 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:40</t>
+    <t xml:space="preserve">2026-09-07 12:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2019.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:57</t>
+    <t xml:space="preserve">2026-09-08 10:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
